--- a/Employee_Reports_wi52/Paul Jeric Azul Falcatan Q0478.xlsx
+++ b/Employee_Reports_wi52/Paul Jeric Azul Falcatan Q0478.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-3</v>
+        <v>-11</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="5" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>693</v>
+        <v>685</v>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -958,11 +958,11 @@
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1056,11 +1056,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>-322</v>
+        <v>-330</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1093,11 +1093,11 @@
         </is>
       </c>
       <c r="H14" s="5" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
@@ -1142,11 +1142,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>-155</v>
+        <v>-163</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1191,11 +1191,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-124</v>
+        <v>-132</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1240,11 +1240,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-155</v>
+        <v>-163</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1289,11 +1289,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>-124</v>
+        <v>-132</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1326,11 +1326,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>-24</v>
+        <v>-32</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1375,11 +1375,11 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1403,20 +1403,20 @@
       <c r="E21" s="4" t="inlineStr"/>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>05-Jul-2025</t>
+          <t>26-Aug-2026</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>05-Jul-2027</t>
+          <t>25-Aug-2028</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>319</v>
+        <v>728</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>7612</v>
+        <v>7604</v>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>7800</v>
+        <v>7792</v>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
